--- a/docs/Generated_paper/question_num_significance_test/paper/test_grammar_2_1_['No. 91_～ば〈条件(じょうけん)〉 ']_revised.xlsx
+++ b/docs/Generated_paper/question_num_significance_test/paper/test_grammar_2_1_['No. 91_～ば〈条件(じょうけん)〉 ']_revised.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,1546 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>: もんだい2 雨が　降れば　試合は　中止に　(   )。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1. なる 2. する 3. いる 4. ある</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>: もんだい2 時間が　あれば　本を　(   )。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1. 読む 2. 書く 3. 見る 4. 作る</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>: もんだい2 お金を　ためれば　新しい　パソコンを　(   )。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1. 買う 2. 売る 3. 借りる 4. 使う</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>: もんだい2 早く　寝れば　朝　元気に　(   )。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1. 起きる 2. 寝る 3. 食べる 4. 行く</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>: もんだい2 仕事が　終われば　友達と　(   )。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1. 遊ぶ 2. 学ぶ 3. 泳ぐ 4. 働く</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>: もんだい2 天気が　良ければ　ピクニックに　(   )。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1. 行く 2. 帰る 3. 来る 4. 戻る</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>: もんだい2 暇が　あれば　映画を　(   )。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1. 見る 2. 聞く 3. 話す 4. 描く</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>: もんだい2 時間が　あれば、手伝いに　(   )。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1. 行く 2. 寝る 3. 立つ 4. 走る</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>: もんだい2 勉強すれば、試験に　(   )。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1. 合格する 2. 失敗する 3. 落ちる 4. 終わる</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>: もんだい2 お金が　あれば、旅行に　(   )。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1. 行く 2. 泊まる 3. 走る 4. 飛ぶ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>: もんだい3 雨が降れば、試合は(   )。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1. 中止だ 2. 中止にする 3. 中止で 4. 中止になる</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>: もんだい3 この薬を飲めば、すぐに(   )。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1. 治る 2. 治らない 3. 治って 4. 治りそう</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>: もんだい3 時間があれば、映画を(   )。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1. 見る 2. 見て 3. 見ます 4. 見ない</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>: もんだい3 お金があれば、あの車を(   )。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1. 買う 2. 買いました 3. 買って 4. 買わない</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>: もんだい3 友達が来れば、パーティーがもっと(   )。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1. 楽しい 2. 楽しむ 3. 楽しんで 4. 楽しくない</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>: もんだい3 天気が良ければ、ピクニックに(   )。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1. 行く 2. 行って 3. 行かない 4. 行こう</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>: もんだい3 もっと勉強すれば、試験に(   )。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1. 合格する 2. 合格して 3. 合格しない 4. 合格だ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>: もんだい3 静かにすれば、赤ちゃんが(   )。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1. 眠る 2. 眠って 3. 眠らない 4. 眠い</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>: もんだい3 運動すれば、健康が(   )。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1. よくなる 2. よい 3. よくない 4. よくして</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>: もんだい3 早く寝れば、朝早く(   )。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1. 起きられる 2. 起きる 3. 起きない 4. 起きて</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　雨が　降れば、　ピクニックは　(   ).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1. 中止したい 2. 中止する 3. 中止しよう 4. 中止した</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>: もんだい4 彼が　来れば、　映画を　一緒に　(   ).</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1. 見よう 2. 見たかった 3. 見たい 4. 見る</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>: もんだい4 この薬を　飲めば、　すぐに　(   ).</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1. よくなりたがる 2. よくなる 3. よくなっている 4. よくなりたい</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　試験に　合格すれば、　大学に　(   ).</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1. 行くことにした 2. 行きたかった 3. 行くつもりだ 4. 行こうと思う</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>: もんだい4 時間が　あれば、　あなたに　手紙を　(   ).</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1. 書く 2. 書くことにした 3. 書きたい 4. 書こうと思う</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　彼女が　来れば、　一緒に　(   ).</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1. 夕食を　食べたい 2. 夕食を　食べたかった 3. 夕食を　食べよう 4. 夕食を　食べる</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>: もんだい4 彼女が　手伝えば、　もっと　早く　(   ).</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1. 終わらせたかった 2. 終わらせたい 3. 終わらせよう 4. 終わらせる</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　お金が　あれば、　新しいスマホを　(   ).</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1. 買いたい 2. 買う 3. 買おう 4. 買うことにした</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>: もんだい4 もっと　練習すれば、　試合に　(   )。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1. 勝ちたがる 2. 勝てる 3. 勝ちたい 4. 勝ちそうだ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>: もんだい4 これを　やれば、　すぐに　終わると　(   ).</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1. 思った 2. 思っている 3. 思いたい 4. 思う</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>: もんだい5 この本は面白いが、あの本　(   )　面白くない。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1. ほど 2. なら 3. しか 4. ばかり</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>: もんだい5 この道をまっすぐ行け　(   )　駅に着きますよ。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>: もんだい5 雨が降らなけれ　(   )　ピクニックに行きます。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>: もんだい5 宿題を終わらせれ　(   )　遊びに行ってもいいです。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1. から 2. ば 3. ほど 4. だけ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>: もんだい5 この映画は怖いが、あの映画　(   )　怖くない。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1. ほど 2. から 3. なら 4. まで</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>: もんだい5 たくさん練習すれ　(   )　上手になります。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>: もんだい5 お金があれ　(   )　旅行に行きたいです。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1. ば 2. から 3. ほど 4. しか</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>: もんだい5 早く寝れ　(   )　明日元気になります。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1. ば 2. から 3. ほど 4. だけ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>: もんだい5 彼は賢いが、彼女　(   )　賢くない。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1. ほど 2. ば 3. から 4. まで</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>: もんだい5 勉強すれ　(   )　するほど、試験が簡単になります。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1. なら 2. ば 3. ほど 4. から</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「雨が降れば、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1. 試合は中止です 2. 試合が中止です 3. 試合を中止です 4. 試合は中止にします</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「この本、面白ければ、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1. 私に貸してください 2. 私に貸してもいいですか 3. 私に貸してくれませんか 4. 私に貸していただけますか</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「時間があれば、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1. 一緒に行きませんか 2. 一緒に行ってもいいですか 3. 一緒に行ってください 4. 一緒に行ってほしいです</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「いい天気なら、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1. 山に登りましょう 2. 山に登ります 3. 山に登ってください 4. 山に登りたいです</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし暇があれば、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1. 映画を見に行きましょうか 2. 映画を見に行ってください 3. 映画を見に行きますか 4. 映画を見に行ってもいいですか</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「風邪を引いたら、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1. 早く寝たほうがいいです 2. 早く寝ますか 3. 早く寝てください 4. 早く寝たらどうですか</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「道が分からなければ、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1. 誰かに聞いてください 2. 誰かに聞きませんか 3. 誰かに聞いてもいいですか 4. 誰かに聞くといいです</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「お金があれば、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1. 新しい車を買いたいです 2. 新しい車を買いますか 3. 新しい車を買ってください 4. 新しい車を買ったらいいです</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「疲れたら、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1. 休んだほうがいいです 2. 休んでください 3. 休みましょう 4. 休んでもいいですか</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「彼が来れば、」 B:「(   )。 」</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1. パーティーを始めます 2. パーティーを始めましょう 3. パーティーを始めてください 4. パーティーを始めてもいいですか</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>: もんだい7 雨が降れば、ピクニックは(   )。</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1. 中止にしよう 2. 中止になる 3. 中止にする 4. 中止できる</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>: もんだい7 あの映画は面白ければ、(   )。</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1. 見ることになる 2. 見たくなる 3. 見なければならない 4. 見よう</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>: もんだい7 勉強すれば、テストに(   )。</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1. 合格できる 2. 合格する 3. 合格しない 4. 合格にならない</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>: もんだい7 このボタンを押せば、(   )。</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1. ドアが開ける 2. ドアが開く 3. ドアを開ける 4. ドアを開かない</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>: もんだい7 この薬を飲めば、(   )。</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1. よくなるかもしれない 2. よくならないかもしれない 3. よくなることにした 4. よくなるつもりだ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>: もんだい7 時間があれば、(   )。</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1. 映画を見たい 2. 映画を見よう 3. 映画を見ようと思う 4. 映画を見てもいい</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>: もんだい7 家に帰れば、(   )。</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1. リラックスできる 2. リラックスしなければならない 3. リラックスしている 4. リラックスしたい</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>: もんだい7 お金があれば、(   )。</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1. 旅行に行こう 2. 旅行に行かない 3. 旅行に行くことになった 4. 旅行に行った</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>: もんだい7 彼が来れば、(   )。</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1. パーティーが始める 2. パーティーを始める 3. パーティーが始まる 4. パーティーを始まる</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>: もんだい7 この本を読めば、(   )。</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1. 話がわかる 2. 話をわかる 3. 話がわからない 4. 話をわからない</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>: もんだい8 雨が降れば、道が(   )なる。</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほど 4. らしく</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>: もんだい8 その子供は、大人の(   )賢い。</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1. ように 2. ほどに 3. らしく 4. みたい</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼女が笑えば、太陽の(   )明るくなる。</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>: もんだい8 もし疲れれば、猫の(   )眠ることができる。</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼が来れば、すべてが(   )解決する。</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1. らしく 2. みたいに 3. ように 4. ほど</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>: もんだい8 この歌を聴けば、昔の(   )思い出す。</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1. ほどに 2. みたいに 3. ように 4. らしく</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼女が手伝えば、仕事が(   )早く終わる。</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>: もんだい8 あの映画を見れば、夢の(   )感じる。</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1. ように 2. ほどに 3. らしく 4. みたいに</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼が説明すれば、子供でも(   )わかる。</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>: もんだい8 この薬を飲めば、魔法の(   )効く。</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
